--- a/OMOP Analysis/Results/Output_yearly_visits_OMOP.xlsx
+++ b/OMOP Analysis/Results/Output_yearly_visits_OMOP.xlsx
@@ -402,25 +402,25 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>11.46</v>
+        <v>14.59</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2">
-        <v>107</v>
+        <v>298</v>
       </c>
       <c r="E2">
-        <v>10.95</v>
+        <v>13.57</v>
       </c>
       <c r="F2">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H2">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3">
@@ -428,25 +428,25 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>12.59</v>
+        <v>6.48</v>
       </c>
       <c r="C3">
         <v>0.5</v>
       </c>
       <c r="D3">
-        <v>200.5</v>
+        <v>76.5</v>
       </c>
       <c r="E3">
-        <v>11.83</v>
+        <v>6.3</v>
       </c>
       <c r="F3">
-        <v>9.5</v>
+        <v>5</v>
       </c>
       <c r="G3">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="H3">
-        <v>16.5</v>
+        <v>8.5</v>
       </c>
     </row>
   </sheetData>
@@ -506,25 +506,25 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>10.93</v>
+        <v>14.1</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>107</v>
+        <v>298</v>
       </c>
       <c r="E2">
-        <v>10.96</v>
+        <v>13.59</v>
       </c>
       <c r="F2">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H2">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3">
@@ -532,25 +532,25 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>12.29</v>
+        <v>6.24</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>200.5</v>
+        <v>76.5</v>
       </c>
       <c r="E3">
-        <v>11.84</v>
+        <v>6.3</v>
       </c>
       <c r="F3">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="G3">
-        <v>4.5</v>
+        <v>2</v>
       </c>
       <c r="H3">
-        <v>16.5</v>
+        <v>8.5</v>
       </c>
     </row>
   </sheetData>

--- a/OMOP Analysis/Results/Output_yearly_visits_OMOP.xlsx
+++ b/OMOP Analysis/Results/Output_yearly_visits_OMOP.xlsx
@@ -402,25 +402,25 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>14.59</v>
+        <v>19</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2">
-        <v>298</v>
+        <v>315</v>
       </c>
       <c r="E2">
-        <v>13.57</v>
+        <v>18.55</v>
       </c>
       <c r="F2">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H2">
-        <v>19</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3">
@@ -428,25 +428,25 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>6.48</v>
+        <v>14.9</v>
       </c>
       <c r="C3">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>76.5</v>
+        <v>209.99</v>
       </c>
       <c r="E3">
-        <v>6.3</v>
+        <v>15.23</v>
       </c>
       <c r="F3">
-        <v>5</v>
+        <v>10.01</v>
       </c>
       <c r="G3">
-        <v>2.5</v>
+        <v>5.01</v>
       </c>
       <c r="H3">
-        <v>8.5</v>
+        <v>19.03</v>
       </c>
     </row>
   </sheetData>
@@ -506,25 +506,25 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>14.1</v>
+        <v>18.32</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>298</v>
+        <v>315</v>
       </c>
       <c r="E2">
-        <v>13.59</v>
+        <v>18.55</v>
       </c>
       <c r="F2">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G2">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="H2">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3">
@@ -532,25 +532,25 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>6.24</v>
+        <v>14.37</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>76.5</v>
+        <v>209.99</v>
       </c>
       <c r="E3">
-        <v>6.3</v>
+        <v>15.21</v>
       </c>
       <c r="F3">
-        <v>4.5</v>
+        <v>10.01</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>5.01</v>
       </c>
       <c r="H3">
-        <v>8.5</v>
+        <v>19.03</v>
       </c>
     </row>
   </sheetData>

--- a/OMOP Analysis/Results/Output_yearly_visits_OMOP.xlsx
+++ b/OMOP Analysis/Results/Output_yearly_visits_OMOP.xlsx
@@ -402,7 +402,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>19</v>
+        <v>20.09</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -411,16 +411,16 @@
         <v>315</v>
       </c>
       <c r="E2">
-        <v>18.55</v>
+        <v>19.29</v>
       </c>
       <c r="F2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H2">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3">
@@ -428,7 +428,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>14.9</v>
+        <v>15.71</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -437,16 +437,16 @@
         <v>209.99</v>
       </c>
       <c r="E3">
-        <v>15.23</v>
+        <v>15.8</v>
       </c>
       <c r="F3">
-        <v>10.01</v>
+        <v>11.02</v>
       </c>
       <c r="G3">
         <v>5.01</v>
       </c>
       <c r="H3">
-        <v>19.03</v>
+        <v>20.97</v>
       </c>
     </row>
   </sheetData>
@@ -506,7 +506,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>18.32</v>
+        <v>19.47</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -515,16 +515,16 @@
         <v>315</v>
       </c>
       <c r="E2">
-        <v>18.55</v>
+        <v>19.31</v>
       </c>
       <c r="F2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G2">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="H2">
-        <v>24</v>
+        <v>25.9</v>
       </c>
     </row>
     <row r="3">
@@ -532,7 +532,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>14.37</v>
+        <v>15.25</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -541,16 +541,16 @@
         <v>209.99</v>
       </c>
       <c r="E3">
-        <v>15.21</v>
+        <v>15.79</v>
       </c>
       <c r="F3">
-        <v>10.01</v>
+        <v>11.02</v>
       </c>
       <c r="G3">
         <v>5.01</v>
       </c>
       <c r="H3">
-        <v>19.03</v>
+        <v>20.03</v>
       </c>
     </row>
   </sheetData>
